--- a/data/trans_dic/IP1022_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP1022_2023-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen otros</t>
+          <t>Menores que padecen otros (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -571,24 +572,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 34,36</t>
+          <t>1,57; 36,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 12,3</t>
+          <t>2,03; 11,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,85; 20,51</t>
+          <t>2,94; 23,44</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -621,24 +622,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,57; 12,38</t>
+          <t>2,67; 12,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,16; 9,79</t>
+          <t>2,34; 9,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,16; 8,77</t>
+          <t>3,35; 9,09</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,52; 12,17</t>
+          <t>2,75; 13,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,03; 16,27</t>
+          <t>5,26; 16,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,17; 12,95</t>
+          <t>5,08; 12,68</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,42; 14,95</t>
+          <t>3,17; 15,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,31; 22,34</t>
+          <t>5,26; 23,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,72; 16,33</t>
+          <t>5,82; 16,15</t>
         </is>
       </c>
     </row>
@@ -771,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 12,46</t>
+          <t>1,55; 13,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 13,16</t>
+          <t>1,32; 13,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,14; 10,67</t>
+          <t>2,21; 10,15</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -821,24 +822,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,0; 17,05</t>
+          <t>4,07; 17,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,24; 17,21</t>
+          <t>4,68; 17,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,63; 14,61</t>
+          <t>5,63; 15,19</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,84; 13,19</t>
+          <t>4,88; 13,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,28; 24,72</t>
+          <t>7,82; 27,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,63; 18,2</t>
+          <t>7,22; 17,65</t>
         </is>
       </c>
     </row>
@@ -921,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,93</t>
+          <t>0,47; 5,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,58; 4,71</t>
+          <t>0,73; 4,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,92</t>
+          <t>0,89; 3,71</t>
         </is>
       </c>
     </row>
@@ -971,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,81; 9,58</t>
+          <t>4,74; 9,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,82; 10,5</t>
+          <t>6,0; 10,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,75; 9,02</t>
+          <t>5,89; 9,2</t>
         </is>
       </c>
     </row>
@@ -1007,4 +1008,750 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen otros (tasa de respuesta: 99,9%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>7571</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4361</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11933</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1152; 26690</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1612; 9380</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4493; 35775</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>8581</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6068</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>14650</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>3382; 15584</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2987; 12256</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>8516; 23118</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>3625</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6712</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10337</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1602; 7831</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3533; 11311</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6374; 15910</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>5447</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9564</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>15012</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2227; 10937</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>4108; 18007</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>8636; 23954</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1650</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2268</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3918</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>534; 4824</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>538; 5406</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1662; 7635</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>4138</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>5409</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>9547</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>1854; 7914</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2631; 9866</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>5732; 15454</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>10426</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>19983</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>30409</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>6076; 16829</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>11868; 41115</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>19944; 48758</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>2365</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>3262</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>5627</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>621; 7041</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>1145; 7425</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>2574; 10703</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>43804</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>57628</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>101432</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>31503; 62818</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>45454; 79980</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>83732; 130841</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1022_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP1022_2023-Provincia-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 36,42</t>
+          <t>1,59; 35,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 11,82</t>
+          <t>2,01; 11,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,94; 23,44</t>
+          <t>3,13; 22,21</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,67; 12,29</t>
+          <t>2,46; 11,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,34; 9,61</t>
+          <t>2,27; 9,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,35; 9,09</t>
+          <t>3,39; 9,14</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,75; 13,44</t>
+          <t>2,61; 12,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,26; 16,84</t>
+          <t>5,4; 17,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,08; 12,68</t>
+          <t>4,54; 12,78</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,17; 15,59</t>
+          <t>3,41; 15,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,26; 23,05</t>
+          <t>5,14; 22,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,82; 16,15</t>
+          <t>5,47; 15,92</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 13,98</t>
+          <t>1,53; 12,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 13,28</t>
+          <t>1,42; 12,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,21; 10,15</t>
+          <t>2,22; 9,83</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,07; 17,37</t>
+          <t>4,21; 17,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,68; 17,56</t>
+          <t>4,7; 17,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,63; 15,19</t>
+          <t>5,24; 14,99</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,88; 13,52</t>
+          <t>4,76; 13,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,82; 27,09</t>
+          <t>7,4; 25,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,22; 17,65</t>
+          <t>7,68; 18,44</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,47; 5,35</t>
+          <t>0,47; 5,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,74</t>
+          <t>0,7; 4,96</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,71</t>
+          <t>0,87; 4,08</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,74; 9,45</t>
+          <t>4,86; 9,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,0; 10,56</t>
+          <t>5,81; 10,36</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,89; 9,2</t>
+          <t>5,85; 9,15</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1152; 26690</t>
+          <t>1166; 25701</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1612; 9380</t>
+          <t>1596; 8983</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4493; 35775</t>
+          <t>4772; 33896</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3382; 15584</t>
+          <t>3126; 15102</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2987; 12256</t>
+          <t>2891; 12211</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8516; 23118</t>
+          <t>8628; 23266</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1602; 7831</t>
+          <t>1521; 7201</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3533; 11311</t>
+          <t>3625; 11943</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6374; 15910</t>
+          <t>5688; 16028</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2227; 10937</t>
+          <t>2392; 10696</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4108; 18007</t>
+          <t>4014; 17499</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8636; 23954</t>
+          <t>8110; 23609</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>534; 4824</t>
+          <t>526; 4472</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>538; 5406</t>
+          <t>577; 5111</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1662; 7635</t>
+          <t>1674; 7392</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1854; 7914</t>
+          <t>1916; 8052</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2631; 9866</t>
+          <t>2641; 10068</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5732; 15454</t>
+          <t>5334; 15253</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>6076; 16829</t>
+          <t>5927; 16971</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>11868; 41115</t>
+          <t>11236; 37991</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19944; 48758</t>
+          <t>21224; 50957</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>621; 7041</t>
+          <t>620; 6802</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1145; 7425</t>
+          <t>1095; 7770</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2574; 10703</t>
+          <t>2522; 11767</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>31503; 62818</t>
+          <t>32300; 64667</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>45454; 79980</t>
+          <t>44031; 78467</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>83732; 130841</t>
+          <t>83249; 130132</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1022_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP1022_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 35,07</t>
+          <t>2,69; 13,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,01; 11,32</t>
+          <t>1,03; 10,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 22,21</t>
+          <t>2,44; 9,2</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,46; 11,91</t>
+          <t>2,04; 9,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,27; 9,57</t>
+          <t>4,55; 15,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,39; 9,14</t>
+          <t>4,01; 10,27</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,61; 12,36</t>
+          <t>4,73; 16,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,4; 17,78</t>
+          <t>2,7; 12,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,54; 12,78</t>
+          <t>5,21; 12,98</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,41; 15,25</t>
+          <t>5,53; 23,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,14; 22,4</t>
+          <t>3,66; 16,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,47; 15,92</t>
+          <t>6,01; 16,71</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 12,96</t>
+          <t>1,47; 12,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 12,55</t>
+          <t>1,53; 12,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,22; 9,83</t>
+          <t>2,15; 10,58</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,21; 17,67</t>
+          <t>4,58; 18,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,7; 17,92</t>
+          <t>3,95; 16,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,24; 14,99</t>
+          <t>5,75; 15,02</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,76; 13,63</t>
+          <t>6,14; 15,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,4; 25,03</t>
+          <t>4,97; 13,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,68; 18,44</t>
+          <t>6,54; 13,02</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,47; 5,17</t>
+          <t>0,58; 4,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,96</t>
+          <t>0,51; 5,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,08</t>
+          <t>0,88; 4,03</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,86; 9,73</t>
+          <t>5,5; 9,08</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,81; 10,36</t>
+          <t>4,89; 8,29</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,85; 9,15</t>
+          <t>5,63; 8,05</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4361</t>
+          <t>2499</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11933</t>
+          <t>6439</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1166; 25701</t>
+          <t>1728; 8358</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1596; 8983</t>
+          <t>582; 6176</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4772; 33896</t>
+          <t>2944; 11096</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>8581</t>
+          <t>5529</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6068</t>
+          <t>8804</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14650</t>
+          <t>14333</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3126; 15102</t>
+          <t>2359; 11404</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2891; 12211</t>
+          <t>4579; 15259</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8628; 23266</t>
+          <t>8668; 22217</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3625</t>
+          <t>5951</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6712</t>
+          <t>3664</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10337</t>
+          <t>9615</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1521; 7201</t>
+          <t>2811; 9516</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3625; 11943</t>
+          <t>1528; 7108</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5688; 16028</t>
+          <t>6041; 15053</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>5447</t>
+          <t>9012</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9564</t>
+          <t>6132</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15012</t>
+          <t>15145</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2392; 10696</t>
+          <t>3994; 16794</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4014; 17499</t>
+          <t>2591; 11725</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8110; 23609</t>
+          <t>8590; 23898</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>2149</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2268</t>
+          <t>1730</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3918</t>
+          <t>3879</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>526; 4472</t>
+          <t>582; 5076</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>577; 5111</t>
+          <t>544; 4511</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1674; 7392</t>
+          <t>1619; 7957</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>4138</t>
+          <t>5051</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5409</t>
+          <t>4066</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9547</t>
+          <t>9117</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1916; 8052</t>
+          <t>2243; 8898</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2641; 10068</t>
+          <t>1782; 7548</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5334; 15253</t>
+          <t>5407; 14121</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>10426</t>
+          <t>14009</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>19983</t>
+          <t>10777</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>30409</t>
+          <t>24786</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5927; 16971</t>
+          <t>8415; 21284</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>11236; 37991</t>
+          <t>6092; 17117</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21224; 50957</t>
+          <t>16963; 33796</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2365</t>
+          <t>3384</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3262</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5627</t>
+          <t>6018</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>620; 6802</t>
+          <t>925; 7848</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1095; 7770</t>
+          <t>721; 7071</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2522; 11767</t>
+          <t>2644; 12080</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>57</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>43804</t>
+          <t>49026</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>57628</t>
+          <t>40307</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>101432</t>
+          <t>89332</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>32300; 64667</t>
+          <t>38275; 63224</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>44031; 78467</t>
+          <t>30744; 52096</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>83249; 130132</t>
+          <t>74610; 106578</t>
         </is>
       </c>
     </row>
